--- a/Participantes_Familia/E01/Keno.xlsx
+++ b/Participantes_Familia/E01/Keno.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eirar\Polla\Participantes\E01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Participantes_Familia\E01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389B7076-E54C-4BC1-8F9A-CA823A0C59E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F74DC7D-E378-4213-946B-38F57BDBE8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -445,27 +445,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -485,6 +464,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -827,43 +827,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831F1176-9B5F-4509-AEB9-C4D2AF7AA58E}">
   <dimension ref="B2:H104"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.53125" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" customWidth="1"/>
-    <col min="3" max="3" width="3.53125" customWidth="1"/>
-    <col min="4" max="4" width="14.73046875" customWidth="1"/>
-    <col min="8" max="8" width="21.796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="4.54296875" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" customWidth="1"/>
+    <col min="3" max="3" width="3.54296875" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" customWidth="1"/>
+    <col min="8" max="8" width="21.81640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="3" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="15" t="s">
+    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
-    </row>
-    <row r="4" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
-    </row>
-    <row r="5" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="6" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="6" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
+    </row>
+    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
+    </row>
+    <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="4" t="s">
         <v>37</v>
       </c>
@@ -878,29 +878,29 @@
         <v>Gana Sudáfrica</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="9" t="s">
+    <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="10" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="6" t="s">
+    <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="4" t="s">
         <v>40</v>
       </c>
@@ -915,29 +915,29 @@
         <v>Gana Paraguay</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+    <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="14" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="6" t="s">
+    <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="4" t="s">
         <v>11</v>
       </c>
@@ -952,29 +952,29 @@
         <v>Gana Marruecos</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="9" t="s">
+    <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="18" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B18" s="6" t="s">
+    <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="4" t="s">
         <v>43</v>
       </c>
@@ -990,29 +990,29 @@
         <v>Gana Turquía</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="9" t="s">
+    <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="22" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="6" t="s">
+    <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="4" t="s">
         <v>45</v>
       </c>
@@ -1027,29 +1027,29 @@
         <v>Gana Japón</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+    <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="26" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B26" s="6" t="s">
+    <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B27" s="4" t="s">
         <v>46</v>
       </c>
@@ -1064,29 +1064,29 @@
         <v>Gana Egipto</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="9" t="s">
+    <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="30" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B30" s="6" t="s">
+    <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="31" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B31" s="4" t="s">
         <v>5</v>
       </c>
@@ -1101,29 +1101,29 @@
         <v>Gana Senegal</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="9" t="s">
+    <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="34" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B34" s="6" t="s">
+    <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="4" t="s">
         <v>10</v>
       </c>
@@ -1138,29 +1138,29 @@
         <v>Gana Argelia</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="9" t="s">
+    <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="38" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B38" s="6" t="s">
+    <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="39" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B39" s="4" t="s">
         <v>49</v>
       </c>
@@ -1176,29 +1176,29 @@
         <v>Gana Croacia</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="9" t="s">
+    <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="42" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B42" s="6" t="s">
+    <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="43" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B43" s="4" t="s">
         <v>37</v>
       </c>
@@ -1213,29 +1213,29 @@
         <v>Gana Corea</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B44" s="9" t="s">
+    <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B44" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="46" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B46" s="6" t="s">
+    <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="47" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="4" t="s">
         <v>40</v>
       </c>
@@ -1250,29 +1250,29 @@
         <v>Gana Australia</v>
       </c>
     </row>
-    <row r="48" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B48" s="9" t="s">
+    <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B48" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="50" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B50" s="6" t="s">
+    <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
       </c>
     </row>
-    <row r="51" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="51" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B51" s="4" t="s">
         <v>45</v>
       </c>
@@ -1287,29 +1287,29 @@
         <v>Gana Suecia</v>
       </c>
     </row>
-    <row r="52" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="9" t="s">
+    <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="54" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B54" s="6" t="s">
+    <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
       </c>
     </row>
-    <row r="55" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="55" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B55" s="4" t="s">
         <v>46</v>
       </c>
@@ -1324,29 +1324,29 @@
         <v>Gana Irán</v>
       </c>
     </row>
-    <row r="56" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B56" s="9" t="s">
+    <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B56" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="58" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B58" s="6" t="s">
+    <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
       </c>
     </row>
-    <row r="59" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="59" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B59" s="4" t="s">
         <v>10</v>
       </c>
@@ -1362,29 +1362,29 @@
         <v>Gana Austria</v>
       </c>
     </row>
-    <row r="60" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B60" s="9" t="s">
+    <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B60" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="62" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B62" s="6" t="s">
+    <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
       </c>
     </row>
-    <row r="63" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="63" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B63" s="4" t="s">
         <v>53</v>
       </c>
@@ -1399,29 +1399,29 @@
         <v>Gana Senegal</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B64" s="9" t="s">
+    <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B64" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="66" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B66" s="6" t="s">
+    <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
       </c>
     </row>
-    <row r="67" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="67" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B67" s="4" t="s">
         <v>54</v>
       </c>
@@ -1436,29 +1436,29 @@
         <v>Gana Canadá</v>
       </c>
     </row>
-    <row r="68" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B68" s="9" t="s">
+    <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B68" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="70" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B70" s="6" t="s">
+    <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
       </c>
     </row>
-    <row r="71" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B71" s="4" t="s">
         <v>56</v>
       </c>
@@ -1473,29 +1473,29 @@
         <v>Gana Alemania</v>
       </c>
     </row>
-    <row r="72" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B72" s="9" t="s">
+    <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B72" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="74" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B74" s="6" t="s">
+    <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
       </c>
     </row>
-    <row r="75" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="75" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B75" s="4" t="s">
         <v>27</v>
       </c>
@@ -1510,29 +1510,29 @@
         <v>Gana Suecia</v>
       </c>
     </row>
-    <row r="76" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B76" s="9" t="s">
+    <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B76" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="78" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B78" s="6" t="s">
+    <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
       </c>
     </row>
-    <row r="79" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="79" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B79" s="4" t="s">
         <v>44</v>
       </c>
@@ -1548,29 +1548,29 @@
         <v>Gana Estados Unidos</v>
       </c>
     </row>
-    <row r="80" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B80" s="9" t="s">
+    <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B80" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="82" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B82" s="6" t="s">
+    <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
       </c>
     </row>
-    <row r="83" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="83" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B83" s="4" t="s">
         <v>41</v>
       </c>
@@ -1585,29 +1585,29 @@
         <v>Gana Australia</v>
       </c>
     </row>
-    <row r="84" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B84" s="9" t="s">
+    <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B84" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="86" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B86" s="6" t="s">
+    <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="87" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B87" s="4" t="s">
         <v>57</v>
       </c>
@@ -1622,29 +1622,29 @@
         <v>Gana España</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B88" s="9" t="s">
+    <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B88" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="90" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B90" s="6" t="s">
+    <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
       </c>
     </row>
-    <row r="91" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="91" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B91" s="4" t="s">
         <v>53</v>
       </c>
@@ -1659,29 +1659,29 @@
         <v>Gana Francia</v>
       </c>
     </row>
-    <row r="92" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B92" s="9" t="s">
+    <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B92" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="94" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B94" s="6" t="s">
+    <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="95" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B95" s="4" t="s">
         <v>47</v>
       </c>
@@ -1696,29 +1696,29 @@
         <v>Gana Irán</v>
       </c>
     </row>
-    <row r="96" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B96" s="9" t="s">
+    <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B96" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="98" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B98" s="6" t="s">
+    <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
       </c>
     </row>
-    <row r="99" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="99" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B99" s="4" t="s">
         <v>48</v>
       </c>
@@ -1733,29 +1733,29 @@
         <v>Gana Austria</v>
       </c>
     </row>
-    <row r="100" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B100" s="9" t="s">
+    <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B100" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="102" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B102" s="6" t="s">
+    <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="103" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B103" s="4" t="s">
         <v>58</v>
       </c>
@@ -1770,12 +1770,12 @@
         <v>Gana Portugal</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B104" s="9" t="s">
+    <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B104" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1783,6 +1783,42 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1799,42 +1835,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Participantes_Familia/E01/Keno.xlsx
+++ b/Participantes_Familia/E01/Keno.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fase de Grupos" sheetId="1" state="visible" r:id="rId1"/>
@@ -173,26 +173,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -218,6 +198,26 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -237,6 +237,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
@@ -258,36 +279,15 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -655,7 +655,7 @@
       <c r="D3" s="20" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" thickBot="1">
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>España</t>
         </is>
@@ -1897,13 +1897,12 @@
   <mergeCells count="52">
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B98:D98"/>
     <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B48:D48"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B78:D78"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
@@ -1913,25 +1912,26 @@
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B74:D74"/>
     <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B36:D36"/>
     <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B36:D36"/>
     <mergeCell ref="B76:D76"/>
     <mergeCell ref="B94:D94"/>
     <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B4:D4"/>
     <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B4:D4"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B100:D100"/>
     <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B86:D86"/>
     <mergeCell ref="B72:D72"/>
     <mergeCell ref="B90:D90"/>
     <mergeCell ref="B3:D3"/>
@@ -1939,14 +1939,14 @@
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="B102:D102"/>
     <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B52:D52"/>
     <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B96:D96"/>
     <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B18:D18"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B48:D48"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B96 B100 B104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
